--- a/División/US_División.xlsx
+++ b/División/US_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>44.01716989988011</v>
+        <v>44.01716989988009</v>
       </c>
       <c r="C2" s="2">
-        <v>115.0086775853638</v>
+        <v>115.0264386249907</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>50.62356501235494</v>
+        <v>50.63138291934347</v>
       </c>
     </row>
     <row r="3" spans="1:5">
